--- a/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
+++ b/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'用例结果'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'缺陷清单'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'缺陷清单'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1487,7 +1487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>待定夺 — 规格未实现的特性，需先定混合价格显示规则</t>
+          <t>已修复（dff4790 + f5f9309）— 接口批量返回价格汇总 + 卡片显示「¥最低价 起 / 互勉 / 面议 / 暂未设置」</t>
         </is>
       </c>
     </row>
@@ -1959,8 +1959,132 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>只挂面议套餐的摄影师会让整个摄影师列表 500</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>C 端 · 摄影师列表 / SQL 聚合</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>把某位摄影师的在架套餐全部改为面议（price 留空）→ 打开摄影师列表</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>该摄影师按「面议」展示，其余摄影师不受影响</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/photographers 返回 500 {"error":"internal server error"}，整页摄影师消失</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>bool_or 会忽略 NULL 输入：当价格逐行都是 NULL 时 "price = 0" 的取值也逐行是 NULL，bool_or 于是整体返回 NULL；Go 侧 HasFree 是 bool，扫描报 "can't scan into dest[2]: cannot scan NULL into *bool"，handler 直接 500。单测喂的是假行数据，照不出这类 NULL 语义 —— 只有连真库才会暴露。</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>server/internal/repository/services.sql.go（getServicePriceSummaries）</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>两个 bool_or 都套 COALESCE(..., false)；补 DB 级集成测试钉住「全面议」与「含互勉」两种组合</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>已修复（dff4790）</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>已修复（dff4790）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>B-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>摄影师改价后 C 端列表最长 5 分钟仍显示旧价</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>缓存 · 摄影师列表 / 套餐</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>GET 一次列表（写满缓存）→ 摄影师改套餐价 → 立刻再 GET 列表</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>改价后列表立即反映新价</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>仍返回旧价（DB 已改成 0 元，接口仍报 399），直到 5 分钟 TTL 自然过期</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>PhotographerHandler.List 把整个响应缓存 5 分钟（key photographers:&lt;keyword&gt;:&lt;location&gt;:&lt;tag&gt;:&lt;page&gt;:&lt;size&gt;），但套餐增/改/删从不失效这个 key —— 正好抵掉「摄影师自助定价」的核心承诺：改完价 C 端看不见。</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>server/internal/handler/photographer_handler.go:32,63 + server/internal/cache/redis.go</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>套餐写入成功后按前缀失效列表缓存（SCAN 游标，不用会阻塞的 KEYS）</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>已修复（0f0fbe7）</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>已修复（0f0fbe7）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1971,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2099,12 +2223,12 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTA(缺陷清单!A2:A8)</f>
+        <f>COUNTA(缺陷清单!A2:A10)</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>值=7</t>
+          <t>值=9</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2239,12 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>COUNTIF(缺陷清单!C2:C8,"高")</f>
+        <f>COUNTIF(缺陷清单!C2:C10,"高")</f>
         <v/>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>值=1</t>
+          <t>值=2</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2255,12 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(缺陷清单!C2:C8,"中")</f>
+        <f>COUNTIF(缺陷清单!C2:C10,"中")</f>
         <v/>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>值=4</t>
+          <t>值=5</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2271,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(缺陷清单!C2:C8,"低")</f>
+        <f>COUNTIF(缺陷清单!C2:C10,"低")</f>
         <v/>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -2163,12 +2287,12 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(缺陷清单!K2:K8,"已修复*")</f>
+        <f>COUNTIF(缺陷清单!K2:K10,"已修复*")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>值=4</t>
+          <t>值=7</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2303,12 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(缺陷清单!K2:K8,"待定夺*")</f>
+        <f>COUNTIF(缺陷清单!K2:K10,"待定夺*")</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>值=2</t>
+          <t>值=1</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2319,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(缺陷清单!K2:K8,"误报*")</f>
+        <f>COUNTIF(缺陷清单!K2:K10,"误报*")</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -2263,7 +2387,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>生成器脚本：.audit/make_report.py（改数据后可重跑再生成）</t>
+          <t>生成器脚本：.audit/make_report.py（本地草稿目录，已 gitignore；改数据后可重跑再生成）</t>
         </is>
       </c>
     </row>
@@ -2274,15 +2398,31 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>B-08 / B-09 不是走查用例发现的，是修复 B-02 时用真库与真实浏览器复核逮到的连带缺陷，一并登记在此。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>B-02 复验：真库 + 浏览器覆盖四个分支 —— ¥399 起（列表页/搜索页）、互勉、面议、暂未设置；首页推荐位（接口不返回价格汇总）完全不显示价格，不把「没查到」说成「暂未设置」。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>
   </mergeCells>

--- a/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
+++ b/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>待定夺 — 产品/隐私决策</t>
+          <t>已修复（ae6339e）— 手机号在 SQL 层按状态遮罩，确认接单后才返回；前端未接单显示「确认接单后可见」</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>值=7</t>
+          <t>值=8</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>值=1</t>
+          <t>值=0</t>
         </is>
       </c>
     </row>
@@ -2412,9 +2412,17 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>B-06 处置（2026-09-24，产品决策=确认接单后才显示）：遮罩写在 SQL 层而非前端，完整号码不再出现在未接单的响应体里；已用浏览器实测跨越那条线——待确认显示「确认接单后可见」，点下「确认接单」状态转「待完成」的同一刻号码出现。覆盖 pending/confirmed/completed/cancelled 的DB 级集成测试已加。此前的建议项「仅提供站内聊天入口」尚未实现（未接单时无联系渠道，待评估）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A22:C22"/>

--- a/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
+++ b/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
@@ -2095,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2415,12 +2415,26 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>B-06 处置（2026-09-24，产品决策=确认接单后才显示）：遮罩写在 SQL 层而非前端，完整号码不再出现在未接单的响应体里；已用浏览器实测跨越那条线——待确认显示「确认接单后可见」，点下「确认接单」状态转「待完成」的同一刻号码出现。覆盖 pending/confirmed/completed/cancelled 的DB 级集成测试已加。此前的建议项「仅提供站内聊天入口」尚未实现（未接单时无联系渠道，待评估）。</t>
+          <t>B-06 处置（2026-09-24，产品决策=确认接单后才显示）：遮罩写在 SQL 层而非前端，完整号码不再出现在未接单的响应体里；已用浏览器实测跨越那条线——待确认显示「确认接单后可见」，点下「确认接单」状态转「待完成」的同一刻号码出现。覆盖 pending/confirmed/completed/cancelled 的DB 级集成测试已加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>B-06 补充实测（2026-09-24，面议/报价路径）：真造了一单面议订单走完整流程——待报价 coserPhone='' → 摄影师报价 ¥888（price_status=quoted，status 仍是 pending）号码仍为 '' → coser 接受报价（转 confirmed/agreed）号码才出现。即「报价 ≠ 成交」，号码卡在成交那一刻，与商品（闲鱼/淘宝）逻辑一致。产品判断：未接单前无需站内联系渠道 —— coser 发需求、摄影师在接单管理里接单即可，故此前建议的「未接单时加联系入口」不做。临时订单/套餐已清理，演示数据回到基线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>B-06 残留不对称（记录待评估，非缺陷）：成交后摄影师拿到 coser 手机号，而 coser 侧没有任何摄影师电话字段（server 内 grep photographerPhone = 0），只能走站内聊天（订单页「联系摄影师」）。若认为成交后应双向交换联系方式，需另开一项。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
@@ -2430,9 +2444,11 @@
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
+++ b/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'用例结果'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'缺陷清单'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'缺陷清单'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1487,7 +1487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2083,8 +2083,380 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>B-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>同一时段可被并发重复预约（缺 DB 约束）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>订单 / 预约核心</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>用线程屏障让 12 个 POST /bookings 同时抢同一摄影师同一 date+time</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>只应有 1 单成功，其余 409</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7 个请求返回 201、7 条订单落在同一时段（顺序请求能正确 409，并发打不穿 —— CountConflictBookings 是先查后插的 TOCTOU）</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>bookings 表只有主键，没有任何 (photographer_id, date, time) 唯一约束；应用层检查在并发下必然失效。一位摄影师同一档期被约 7 次。</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>server/migrations/000029_integrity_constraints.up.sql + booking_service.Create</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>部分唯一索引 uniq_bookings_active_slot（WHERE status &lt;&gt; 'cancelled'，取消释放时段）+ 把 23505 映射成 409</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>已修复 — 复测 12 并发：1 个 201、11 个 409、落库 1 条</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>已修复 — 时段唯一约束（部分唯一索引）+ 23505→409</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>可以预约已经过去的日期（且预约页默认日期会落在昨天）</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>订单 / 预约核心</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>POST /bookings 传 date=2020-01-01；或本地时间早 8 点前打开预约页看默认日期</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>服务端拒绝过去档期；默认日期为本地今天</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>过去日期下单返回 201 并落库；前端用 new Date().toISOString() 取日期（UTC），东八区 00:00-08:00 会取到昨天，一进页面就默认选中过去的一天</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>服务端 Create 只校验日期格式；前端 booking/index.vue:118 用了 toISOString 取本地日期；日期选择器也没有 start 下限</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>server/internal/service/booking_service.go（isPastSlot）+ src/utils/date.ts + booking 页</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>服务端按服务器本地时区拒绝过去档期（今天是硬约束，时刻尽力而为）；前端新增本地日期工具并给 picker 加 :start</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>已修复 — 过去日期/今天已过时刻均 400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>已修复 — 服务端拒绝过去日期/时刻；前端改用本地日期并给选择器加下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>摄影师可以预约自己的套餐（自成交）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>订单 / 业务逻辑</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>以摄影师 5 的账号 POST /bookings 预约摄影师 5 自己的套餐</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>拒绝 —— 自成交无业务含义</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>201 创建成功，订单的 coser 就是该摄影师本人</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Create 只校验套餐归属与黑名单，没有比较下单人与摄影师 owner；自成交会污染单量，并为「自己给自己评价」铺路</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>server/internal/service/booking_service.go（ErrSelfBooking）</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>下单人 == 摄影师 owner 时返回 400</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>已修复</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>已修复 — 禁止摄影师预约自己的套餐</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>B-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>评价没有任何前置校验，且评分/评价数从不更新</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>评价 / 商家信誉</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>未与该摄影师成交过的账号 POST /reviews；或同一人对同一摄影师重复评价</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>只有已完成订单可评价，且一人一评</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>任何登录用户都能给任何摄影师评价，且可无限重复；更关键的是 photographers.rating / review_count 从不随评价更新 —— 列表显示 4.9 分 / 234 条评价，而该摄影师真实只有 3 条评价</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>ReviewService.Create 直接 INSERT；reviews 表无唯一约束；没有触发器、也没有任何聚合更新代码，两个评分字段是种子数据里的死数字</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>server/internal/service/review_service.go + repository/reviews.sql.go + 迁移 000029</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>① 校验存在已完成订单 ② 不能自评 ③ 唯一索引（photographer_id, user_id）兜重复 ④ 每次评价后按 reviews 重算评分与评价数</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>已修复 — 未成交评价 403、重复评价 409、评价成功后评分按事实重算（实测 4.3 / 3 条）</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>已修复 — 评价需已完成订单 + 一人一评 + 评分/评价数按事实重算</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>B-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>摄影师列表的筛选栏全部无效（4 个筛选返回同一结果）</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>C 端 · 摄影师列表</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>打开 摄影师 列表，依次点 热门 / 评分最高 / 接单最多 / 最新入驻</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>四种排序应给出不同顺序</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>只有高亮变化，结果完全一样</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>list.vue 的 setFilter 只改 currentFilter 就重新 loadData，而 loadData 只发 page/size；后端 List 也不接受任何排序参数（SQL 里固定 ORDER BY rating, order_count）</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>src/pages/photographer/list.vue + repository/photographers.sql.go</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>新增 sort 参数（CASE 参数绑定，非字符串拼接）并接进缓存键；同时补 p.id DESC 作为稳定 tiebreaker（排序键不唯一时 LIMIT/OFFSET 翻页会重复/漏行）</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>已修复 — 接口层与 DB 集成测试验证四种排序；演示数据恰好单调，区分度由交叉夹具数据证明</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>已修复 — 筛选键接到服务端排序（sort），并补稳定分页 tiebreaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>B-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>非会话成员也能标记别人的会话「已读」</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>聊天 / 越权（自伤）</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>以不在会话 1 的用户 POST /chat/sessions/1/read</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>403 —— 与 ListMessages / SendMessage 口径一致</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>200 {ok:true}，并给自己写了一条无意义的 chat_read_state 行</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>ChatService.MarkSessionRead 直通 repository，没有 assertParticipant（同文件另外两个入口都有）；影响仅限调用者自己的状态，无跨用户泄露</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>server/internal/service/chat_service.go</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>补 assertParticipant，handler 映射 403/404</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>已修复 — 复测 403</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>已修复 — 非会话成员标记已读改为 403</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2095,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2223,12 +2595,12 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTA(缺陷清单!A2:A10)</f>
+        <f>COUNTA(缺陷清单!A2:A16)</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>值=9</t>
+          <t>值=15</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2611,12 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>COUNTIF(缺陷清单!C2:C10,"高")</f>
+        <f>COUNTIF(缺陷清单!C2:C16,"高")</f>
         <v/>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>值=2</t>
+          <t>值=3</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2627,12 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(缺陷清单!C2:C10,"中")</f>
+        <f>COUNTIF(缺陷清单!C2:C16,"中")</f>
         <v/>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>值=5</t>
+          <t>值=8</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2643,12 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(缺陷清单!C2:C10,"低")</f>
+        <f>COUNTIF(缺陷清单!C2:C16,"低")</f>
         <v/>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>值=2</t>
+          <t>值=4</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2659,12 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(缺陷清单!K2:K10,"已修复*")</f>
+        <f>COUNTIF(缺陷清单!K2:K16,"已修复*")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>值=8</t>
+          <t>值=14</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2675,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(缺陷清单!K2:K10,"待定夺*")</f>
+        <f>COUNTIF(缺陷清单!K2:K16,"待定夺*")</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -2319,7 +2691,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(缺陷清单!K2:K10,"误报*")</f>
+        <f>COUNTIF(缺陷清单!K2:K16,"误报*")</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -2433,12 +2805,36 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>第二轮整体 review（2026-09-24，业务逻辑 + 核心功能）新增 B-10~B-15 六个缺陷，全部已修复并复测。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>越权面专项核查（跨账号对抗测试）：15 项「用 A 的 token 读写 B 的资源」全部 403/404 —— 订单读取与改状态、跨摄影师读接单、非本人会话读消息/发消息、收藏/关注/通知的越权写，均已正确拒绝；其中 favorites / follows / chat_read_state 三项探针最初显示 200/201，经查是**探针误报**（handler 忽略 body 里的 userId、一律用 token 身份，落库归属正确），不构成缺陷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>待你定夺（数据决策，非缺陷）：photographers.rating / review_count 是种子数字，与 reviews 表脱钩（示例：光影行者显示 4.9 / 234 条，真实只有 3 条）。B-13 已让它们**在每次新评价时按事实重算**，所以新评价一到就会自我修正；是否要把现有数据一次性回填成真实值（评分与评价数会显著变小），属演示数据取舍，未擅自改动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>

--- a/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
+++ b/docs/qa/2026-09-24-C端角色扮演整体测试-报告.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'用例结果'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'缺陷清单'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'缺陷清单'!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1487,7 +1487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2455,8 +2455,70 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>B-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>「N单已接」是死数字，订单完成/取消都不更新</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>摄影师信誉 / 展示数据</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>完成或取消一单后看摄影师卡片/详情/列表排序用的单量</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>单量应随真实完成的订单变化</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>order_count 从 seed 起就固定（567/423/312/678/20），订单流转从不更新它；而「接单最多」与默认排序都在用它 —— 等于按一个假数字排序</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>全仓 grep 无任何 order_count 的写入（无触发器、无聚合更新），只有读取点</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>server/internal/repository/reviews.sql.go（RecomputePhotographerStats）+ booking_service 流转路径</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>重算扩到三个字段（rating/review_count/order_count），在订单状态流转与评价写入后调用；历史数据由迁移 000030 一次性回填</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>已修复 — 实测：确认不变、完成后 1→2、取消也会回算；与真实完成单数一致</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>已修复 — 单量随状态流转重算，历史数据已回填（迁移 000030）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2467,7 +2529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2595,12 +2657,12 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTA(缺陷清单!A2:A16)</f>
+        <f>COUNTA(缺陷清单!A2:A17)</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>值=15</t>
+          <t>值=16</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2673,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>COUNTIF(缺陷清单!C2:C16,"高")</f>
+        <f>COUNTIF(缺陷清单!C2:C17,"高")</f>
         <v/>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2627,12 +2689,12 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(缺陷清单!C2:C16,"中")</f>
+        <f>COUNTIF(缺陷清单!C2:C17,"中")</f>
         <v/>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>值=8</t>
+          <t>值=9</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2705,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(缺陷清单!C2:C16,"低")</f>
+        <f>COUNTIF(缺陷清单!C2:C17,"低")</f>
         <v/>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -2659,12 +2721,12 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(缺陷清单!K2:K16,"已修复*")</f>
+        <f>COUNTIF(缺陷清单!K2:K17,"已修复*")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>值=14</t>
+          <t>值=15</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2737,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(缺陷清单!K2:K16,"待定夺*")</f>
+        <f>COUNTIF(缺陷清单!K2:K17,"待定夺*")</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -2691,7 +2753,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(缺陷清单!K2:K16,"误报*")</f>
+        <f>COUNTIF(缺陷清单!K2:K17,"误报*")</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -2808,43 +2870,59 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>第二轮整体 review（2026-09-24，业务逻辑 + 核心功能）新增 B-10~B-15 六个缺陷，全部已修复并复测。</t>
+          <t>第二轮整体 review（2026-09-24，业务逻辑 + 核心功能）新增 B-10~B-16 七个缺陷，全部已修复并复测。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>越权面专项核查（跨账号对抗测试）：15 项「用 A 的 token 读写 B 的资源」全部 403/404 —— 订单读取与改状态、跨摄影师读接单、非本人会话读消息/发消息、收藏/关注/通知的越权写，均已正确拒绝；其中 favorites / follows / chat_read_state 三项探针最初显示 200/201，经查是**探针误报**（handler 忽略 body 里的 userId、一律用 token 身份，落库归属正确），不构成缺陷。</t>
+          <t>展示数据回填（迁移 000030，B-13/B-16）：photographers 的 rating / review_count / order_count 此前是与事实脱钩的种子死数字，已一次性回填成真实值。回填前后对比（光影行者）4.9 分/234 条/567 单 → 5.0 分/2 条/1 单；暗夜骑士 4.7/156/312 → 0 分/0 条/1 单。数字变小是有意为之 —— 它们现在说真话。若要让演示数据重新「丰满」，正确做法是补真实的评价与订单，而不是改回假数字；迁移的 down 是空操作（派生数据没有有意义的逆操作）。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
+          <t>配套：没有评价时后端返回 rating=0 / reviewCount=0，前端卡片与详情页改显示「暂无评分」（直接显示「★ 0」会被读成被打了 0 分）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>越权面专项核查（跨账号对抗测试）：15 项「用 A 的 token 读写 B 的资源」全部 403/404 —— 订单读取与改状态、跨摄影师读接单、非本人会话读消息/发消息、收藏/关注/通知的越权写，均已正确拒绝；其中 favorites / follows / chat_read_state 三项探针最初显示 200/201，经查是**探针误报**（handler 忽略 body 里的 userId、一律用 token 身份，落库归属正确），不构成缺陷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
           <t>待你定夺（数据决策，非缺陷）：photographers.rating / review_count 是种子数字，与 reviews 表脱钩（示例：光影行者显示 4.9 / 234 条，真实只有 3 条）。B-13 已让它们**在每次新评价时按事实重算**，所以新评价一到就会自我修正；是否要把现有数据一次性回填成真实值（评分与评价数会显著变小），属演示数据取舍，未擅自改动。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
